--- a/asignaturas/quimica/propuesta/Propuesta_Quimica_G05-G08.xlsx
+++ b/asignaturas/quimica/propuesta/Propuesta_Quimica_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>El átomo y sus partículas (3.2 a 3.5) se enseñan en 5.° antes del modelo de partículas, que hoy llega en 6.°. Un tema introductorio al inicio de la unidad ordena la secuencia. Se paga con la fusión 9.</t>
+          <t>El átomo y sus partículas (3.2 a 3.5) se enseñan en 5.° antes del modelo de partículas, que hoy llega en 6.° (4.8). Un tema introductorio al inicio de la unidad ordena la secuencia. Se paga con la fusión 10.</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra. (junto a 6.14)</t>
+          <t>6. Ciencias de la Tierra. (unidad compartida con Ciencias de la Tierra y del Espacio)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CO 4, SG 5, UY 5 (Composición del aire y contaminantes atmosféricos); bloqueo: La atmósfera y su composición (sin grado en El Salvador; se introduce primero en el mismo tema)</t>
+          <t>CO 4.5, SG 5, UY 5 (Composición del aire y contaminantes atmosféricos)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Los tres países lo enseñan entre 4.° y 5.°; El Salvador, en 7.° y sin un tema de química asociado. El tema abre con la composición de la atmósfera, su bloqueo. Se paga con la fusión 10.</t>
+          <t>Colombia, Singapur y Uruguay lo enseñan entre 4.° y 5.°; El Salvador, en 7.° y sin un tema de química asociado. El tema abre con la composición de la atmósfera. Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>4. Interacciones químicas. (después de 4.11 y 4.2)</t>
+          <t>4. Interacciones químicas. (4.12 después de 4.11; 4.13 después de 4.2)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Las fórmulas y la interacción iónica se enseñan en 5.° antes de saber qué es un compuesto y qué es un enlace. Pasan a 6.°, a la unidad de enlaces, después de las acciones 5 y 6 y del enlace iónico (4.2).</t>
+          <t>Las fórmulas y la interacción iónica se enseñan en 5.° antes de saber qué es un compuesto y qué es un enlace. Pasan a la unidad de enlaces de 6.°, después de las acciones 5 y 6 y del enlace iónico (4.2).</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>CO 6, UY 5 (Sustancias puras: elementos y compuestos); prerrequisito: Modelo de partículas de la materia (6.°, y 5.° con la acción 1); T8_27 (mover_antes, destino 6.°; hoy en G10-QUI-U1-1.13)</t>
+          <t>AU 6, CO 6, ENG 6, UY 5 (Sustancias puras: elementos y compuestos); prerrequisito: Modelo de partículas de la materia (5.° con la acción 1); mover_antes: destino 6.°; hoy en G10-QUI-U1-1.13</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Colombia y Uruguay lo enseñan en 5.° y 6.°; El Salvador, en 10.°. Es prerrequisito de fórmulas y moléculas. Se ubica en 6.°, tras el modelo de partículas. Se paga con la fusión 11.</t>
+          <t>Los cuatro países, incluidos Inglaterra y Australia, lo enseñan en 5.° o 6.°; El Salvador, en 10.°. Es prerrequisito de fórmulas y moléculas. Se paga con la fusión 12.</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>CO 6, UY 9 (Enlace químico); prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico, Enlace covalente y Enlace metálico (6.°), brecha 4, confianza alta</t>
+          <t>CO 6.5, UY 9 (Enlace químico); prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico, Enlace covalente y Enlace metálico (6.°), brecha 4, confianza alta</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Los tipos de enlace (4.2 a 4.4) llegan en 6.° sin la idea general de enlace, que hoy aparece en 10.°. Se introduce en el primer tema de la unidad, como en Colombia (6.°), sin gastar presupuesto.</t>
+          <t>Los tipos de enlace (4.2 a 4.4) llegan en 6.° sin la idea general de enlace, que hoy aparece en 10.°. Se introduce en el primer tema de la unidad, sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Conservación de la masa (hoy en 10.°) de Ecuación química y su balanceo (7.°), brecha 3, confianza alta; prerrequisito: Reacción química y sus evidencias (4.9, 6.°)</t>
+          <t>ENG 6, AU 8, CO 8, UY 9 (Conservación de la masa); prerrequisito: Conservación de la masa (hoy en 10.°) de Ecuación química y su balanceo (7.°), brecha 3, confianza alta</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>En 7.° se balancean ecuaciones en cuatro temas (1.2, 1.5, 1.8, 1.11) sin haber visto la ley que da sentido al balanceo. Un experimento en 6.° lo resuelve. Se paga con la fusión 12.</t>
+          <t>En 7.° se balancean ecuaciones en cuatro temas sin la ley que da sentido al balanceo. Inglaterra la enseña en 6.°; el destino sugerido (8.°) llegaría tarde para el balanceo. Se paga con la fusión 13.</t>
         </is>
       </c>
     </row>
@@ -892,51 +892,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>G06-CIE-U5-5.2</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>4. Interacciones químicas. (después de 4.14; la unidad 2 de 6.°, Calor y temperatura, va antes)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>5.2. Experimentación con la actividad enzimática y explicación cualitativa de cómo un catalizador facilita el inicio de una reacción.</t>
+          <t>4.15. Clasificación experimental de reacciones exotérmicas y endotérmicas según el cambio de temperatura.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Compara la descomposición del agua oxigenada con y sin papa o hígado y explica, con un diagrama de «colina» de energía, que el catalizador reduce la energía necesaria para iniciar la reacción sin consumirse.</t>
+          <t>Mide la temperatura antes y después de dos reacciones (vinagre y bicarbonato; agua y cloruro de calcio) y clasifica cada una como exotérmica o endotérmica, explicando hacia dónde se transfiere el calor.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Catalizadores, Factores que afectan la rapidez de reacción, Energía de activación y perfil energético</t>
+          <t>Reacciones exotérmicas y endotérmicas, Calor como energía en tránsito, Clasificación de las reacciones químicas</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Energía de activación y perfil energético (hoy en 10.°) de Catalizadores (6.°), brecha 4, confianza alta</t>
+          <t>ENG 6, AU 7 (Reacciones exotérmicas y endotérmicas); bloqueo: Calor como energía en tránsito (hoy en 10.°; se retoma de forma explícita en el mismo tema)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>El tema usa catalizadores sin la idea de energía de activación. Se introduce de forma cualitativa dentro del mismo tema; el perfil energético formal sigue en 10.°.</t>
+          <t>Inglaterra y Australia lo enseñan en 6.° y 7.°; El Salvador, en 10.°. Completa la clasificación de reacciones (4.10) con el criterio energético. Se paga con la fusión 14.</t>
         </is>
       </c>
     </row>
@@ -946,51 +940,45 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>G08-CIE-U4-4.18, G08-CIE-U4-4.19</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4. Estequiometría y dispersiones</t>
+          <t>4. Estequiometría y dispersiones. (después de 4.7)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4.18. Demostración experimental de las propiedades coligativas.</t>
+          <t>4.21. Análisis de la combustión como reacción química: reactivos, productos y energía liberada.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Comprueba con un experimento el descenso del punto de congelación o el aumento del punto de ebullición al agregar soluto y lo explica con el número de partículas disueltas.</t>
+          <t>Escribe y balancea la ecuación de combustión del metano o del etanol, calcula la masa de CO2 producida y relaciona la combustión incompleta con el monóxido de carbono.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Combustión, Estequiometría, Reacciones exotérmicas y endotérmicas</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Propiedades coligativas (4.20 también)</t>
+          <t>AU 8, CO 8.5, ENG 6 (Combustión); prerrequisito: Reacciones exotérmicas y endotérmicas (6.°, acción 8)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Demostración y experimentación de las propiedades coligativas son el mismo contenido en dos temas, con un tercero (4.20) de aplicaciones. La fusión paga la acción 1.</t>
+          <t>Los tres países enseñan la combustión entre 6.° y 8.5; El Salvador, en 11.°. En 8.° une estequiometría, energía y los contaminantes del aire vistos en 5.°. Se paga con la fusión 15.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +993,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.4, G08-CIE-U4-4.5</t>
+          <t>G08-CIE-U4-4.18, G08-CIE-U4-4.19</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1024,27 +1012,27 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>4.4. Interpretación del número de Avogadro y cálculo de partículas y moles de una sustancia.</t>
+          <t>4.18. Demostración experimental de las propiedades coligativas.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Explica el mol como una cantidad fija de partículas y convierte entre moles y número de partículas en problemas sencillos.</t>
+          <t>Comprueba con un experimento el descenso del punto de congelación o el aumento del punto de ebullición al agregar soluto y lo explica con el número de partículas disueltas.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Mol y número de Avogadro (4.10 también)</t>
+          <t>fusión: ambos temas trabajan Propiedades coligativas (4.20 también)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>El significado del número de Avogadro y su uso en cálculos se enseñan mejor juntos. La fusión paga la acción 3.</t>
+          <t>Demostración y experimentación de las propiedades coligativas son el mismo contenido en dos temas, con un tercero (4.20) de aplicaciones. La fusión paga la acción 1.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1047,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.12, G08-CIE-U4-4.14</t>
+          <t>G08-CIE-U4-4.4, G08-CIE-U4-4.5</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -1078,27 +1066,27 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4.12. Identificación de los tipos de dispersiones químicas en sustancias de uso cotidiano y de sus aplicaciones.</t>
+          <t>4.4. Interpretación del número de Avogadro y cálculo de partículas y moles de una sustancia.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Identifica disoluciones, coloides y suspensiones en productos del hogar y describe un uso de cada tipo.</t>
+          <t>Explica el mol como una cantidad fija de partículas y convierte entre moles y número de partículas en problemas sencillos.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Disoluciones, coloides y suspensiones (4.13 también)</t>
+          <t>fusión: ambos temas trabajan Mol y número de Avogadro (4.10 también)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>La unidad dedica tres temas a las dispersiones (4.12, 4.13 y 4.14). Identificación y exploración de aplicaciones se unen; la clasificación (4.13) se mantiene. La fusión paga la acción 5.</t>
+          <t>El significado del número de Avogadro y su uso en cálculos se enseñan mejor juntos. La fusión paga la acción 3.</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1101,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.1, G08-CIE-U4-4.3</t>
+          <t>G08-CIE-U4-4.12, G08-CIE-U4-4.14</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1132,27 +1120,27 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4.1. Identificación de las unidades físicas de concentración y de sus aplicaciones cotidianas, industriales y ambientales.</t>
+          <t>4.12. Identificación de los tipos de dispersiones químicas en sustancias de uso cotidiano y de sus aplicaciones.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Interpreta la concentración en etiquetas de productos (% m/m, % m/v, ppm) y explica su importancia en un caso ambiental o industrial.</t>
+          <t>Identifica disoluciones, coloides y suspensiones en productos del hogar y describe un uso de cada tipo.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Soluto, disolvente y concentración</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Soluto, disolvente y concentración (4.2 y 4.15 también)</t>
+          <t>fusión: ambos temas trabajan Disoluciones, coloides y suspensiones (4.13 también)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Identificar las unidades físicas de concentración y explorar sus aplicaciones son el mismo contenido; el cálculo (4.2) se mantiene aparte. La fusión paga la acción 7.</t>
+          <t>La unidad dedica tres temas a las dispersiones. Identificación y exploración de aplicaciones se unen; la clasificación (4.13) se mantiene. La fusión paga la acción 5.</t>
         </is>
       </c>
     </row>
@@ -1162,16 +1150,16 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.17</t>
+          <t>G08-CIE-U4-4.1, G08-CIE-U4-4.3</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>8</v>
@@ -1186,27 +1174,135 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4.17. Representación de las atracciones entre partículas de soluto y disolvente y de su relación con los factores que afectan la solubilidad.</t>
+          <t>4.1. Identificación de las unidades físicas de concentración y de sus aplicaciones cotidianas, industriales y ambientales.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Explica con dibujos de partículas por qué la sal se disuelve en agua y el aceite no, usando las atracciones entre partículas, y relaciona la temperatura y la agitación con la rapidez de disolución.</t>
+          <t>Interpreta la concentración en etiquetas de productos (% m/m, % m/v, ppm) y explica su importancia en un caso ambiental o industrial.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Fuerzas intermoleculares, Modelo de partículas de la materia, Proceso de disolución y solvatación, Solubilidad y disoluciones saturadas</t>
+          <t>Soluto, disolvente y concentración</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Fuerzas intermoleculares (hoy en 10.°) de Proceso de disolución y solvatación (8.°), brecha 2, confianza alta</t>
+          <t>fusión: ambos temas trabajan Soluto, disolvente y concentración (4.2 y 4.15 también)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>La solvatación exige las fuerzas intermoleculares. Se reformula el tema para retomarlas de forma explícita y cualitativa antes de explicar la disolución, sin gastar presupuesto.</t>
+          <t>Identificar las unidades físicas de concentración y explorar sus aplicaciones son el mismo contenido; el cálculo (4.2) se mantiene aparte. La fusión paga la acción 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>G08-CIE-U4-4.7, G08-CIE-U4-4.8</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>4. Estequiometría y dispersiones</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>4.7. Ejecución e interpretación de cálculos estequiométricos para determinar cantidades de sustancia en gramos.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Calcula la masa de producto o reactivo en una reacción balanceada y juzga si el resultado es razonable.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Estequiometría</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Estequiometría</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Calcular e interpretar el resultado son pasos del mismo procedimiento. La fusión paga la acción 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>G08-CIE-U5-5.5, G08-CIE-U5-5.6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5. Minerales</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5.5. Determinación del hábito cristalino de un mineral preparado experimentalmente y reconocimiento de las estructuras cristalinas.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Compara el cristal que obtuvo con imágenes de minerales y describe su forma geométrica y la estructura cristalina que la explica.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Minerales: composición y estructura cristalina, Sólidos cristalinos y amorfos</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Minerales: composición y estructura cristalina y Sólidos cristalinos y amorfos (5.4 también)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Los temas 5.4 a 5.6 trabajan los mismos dos conceptos. Unir hábito y estructura cristalina libera un tema para la combustión (acción 9).</t>
         </is>
       </c>
     </row>
@@ -1269,10 +1365,10 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1295,7 +1391,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1341,7 +1437,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>

--- a/asignaturas/quimica/propuesta/Propuesta_Quimica_G05-G08.xlsx
+++ b/asignaturas/quimica/propuesta/Propuesta_Quimica_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Modelo de partículas de la materia (hoy en 6.°) de Átomo y partículas subatómicas (5.°), confianza alta; prerrequisito: Modelo de partículas de la materia (bloqueo de Sustancias puras: elementos y compuestos)</t>
+          <t>prerrequisito: Modelo de partículas de la materia (hoy en 6.°) de Átomo y partículas subatómicas (5.°), confianza alta; bloqueo: Modelo de partículas de la materia (6.°) de Sustancias puras: elementos y compuestos (destino 6.°)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>El átomo y sus partículas (3.2 a 3.5) se enseñan en 5.° antes del modelo de partículas, que hoy llega en 6.° (4.8). Un tema introductorio al inicio de la unidad ordena la secuencia. Se paga con la fusión 10.</t>
+          <t>El átomo y sus partículas (3.2 a 3.5) se enseñan en 5.° antes del modelo de partículas, que hoy llega en 6.° (4.8). Un tema introductorio al inicio de la unidad ordena la secuencia. Se paga con la fusión 12.</t>
         </is>
       </c>
     </row>
@@ -673,12 +673,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CO 4.5, SG 5, UY 5 (Composición del aire y contaminantes atmosféricos)</t>
+          <t>CO 4.5, JP 5, SG 5, UY 5 (Composición del aire y contaminantes atmosféricos); mover_antes: destino 5.°, hoy en 7.°, sin bloqueos</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Colombia, Singapur y Uruguay lo enseñan entre 4.° y 5.°; El Salvador, en 7.° y sin un tema de química asociado. El tema abre con la composición de la atmósfera. Se paga con la fusión 11.</t>
+          <t>Japón y Singapur (alto desempeño), con Colombia y Uruguay, lo enseñan entre 4.° y 5.°; El Salvador, en 7.° sin tema de química. Abre con la composición de la atmósfera. Se paga con la fusión 13.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Sustancias puras: elementos y compuestos (hoy en 10.°) de Moléculas y fórmulas químicas (5.°), brecha 5, confianza alta; prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico (5.°), brecha 5, confianza alta</t>
+          <t>prerrequisito: Sustancias puras: elementos y compuestos (hoy en 8.°) de Moléculas y fórmulas químicas (5.°), brecha 3, confianza alta; prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico (5.°), brecha 5, confianza alta</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
@@ -775,12 +775,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>AU 6, CO 6, ENG 6, UY 5 (Sustancias puras: elementos y compuestos); prerrequisito: Modelo de partículas de la materia (5.° con la acción 1); mover_antes: destino 6.°; hoy en G10-QUI-U1-1.13</t>
+          <t>AU 6, CO 6, ENG 6, JP 7, UY 5 (Sustancias puras: elementos y compuestos); mover_antes: destino 6.°, hoy en 8.° (solo dentro de Minerales, G08 5.3); bloqueo: Modelo de partículas de la materia (5.° con la acción 1)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Los cuatro países, incluidos Inglaterra y Australia, lo enseñan en 5.° o 6.°; El Salvador, en 10.°. Es prerrequisito de fórmulas y moléculas. Se paga con la fusión 12.</t>
+          <t>Tres países de alto desempeño (AU, ENG, JP) lo enseñan en 6.° o 7.°; El Salvador, de pasada en 8.° (minerales). Es prerrequisito de fórmulas y moléculas. Se paga con la fusión 14.</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>CO 6.5, UY 9 (Enlace químico); prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico, Enlace covalente y Enlace metálico (6.°), brecha 4, confianza alta</t>
+          <t>CO 6.5, UY 9 (Enlace químico); mover_antes: destino 8.°, hoy en 10.°; prerrequisito: Enlace químico (hoy en 10.°) de Enlace iónico, Enlace covalente y Enlace metálico (6.°), brecha 4, confianza alta</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ENG 6, AU 8, CO 8, UY 9 (Conservación de la masa); prerrequisito: Conservación de la masa (hoy en 10.°) de Ecuación química y su balanceo (7.°), brecha 3, confianza alta</t>
+          <t>AU 8, CO 8, ENG 6, JP 2, UY 9 (Conservación de la masa); mover_antes: destino 8.°, hoy en 10.°; prerrequisito: Conservación de la masa (hoy en 10.°) de Ecuación química y su balanceo (7.°), brecha 3, confianza alta</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>En 7.° se balancean ecuaciones en cuatro temas sin la ley que da sentido al balanceo. Inglaterra la enseña en 6.°; el destino sugerido (8.°) llegaría tarde para el balanceo. Se paga con la fusión 13.</t>
+          <t>En 7.° se balancean ecuaciones sin la ley que da sentido al balanceo. Japón la inicia en primaria e Inglaterra en 6.°; el destino sugerido (8.°) llegaría después del balanceo. Se paga con la fusión 15.</t>
         </is>
       </c>
     </row>
@@ -901,16 +901,16 @@
       </c>
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>4. Interacciones químicas. (después de 4.14; la unidad 2 de 6.°, Calor y temperatura, va antes)</t>
+          <t>1. Compuestos inorgánicos (al final de la unidad, después de 1.12)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>4.15. Clasificación experimental de reacciones exotérmicas y endotérmicas según el cambio de temperatura.</t>
+          <t>1.14. Clasificación experimental de reacciones exotérmicas y endotérmicas según el cambio de temperatura.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>ENG 6, AU 7 (Reacciones exotérmicas y endotérmicas); bloqueo: Calor como energía en tránsito (hoy en 10.°; se retoma de forma explícita en el mismo tema)</t>
+          <t>AU 7, ENG 6, JP 7 (Reacciones exotérmicas y endotérmicas); mover_antes: destino 7.°, hoy en 10.°; bloqueo: Calor como energía en tránsito (hoy en 10.°; la unidad 2 de 6.°, de Física, lo trabaja y se retoma de forma explícita en el mismo tema)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Inglaterra y Australia lo enseñan en 6.° y 7.°; El Salvador, en 10.°. Completa la clasificación de reacciones (4.10) con el criterio energético. Se paga con la fusión 14.</t>
+          <t>Ajustada: pasa de 6.° a 7.°. Con Japón, tres países de alto desempeño la enseñan y la mediana es 7.°. Cierra la unidad de reacciones de 7.°. Se paga con la fusión 16.</t>
         </is>
       </c>
     </row>
@@ -949,36 +949,36 @@
       </c>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4. Estequiometría y dispersiones. (después de 4.7)</t>
+          <t>1. Compuestos inorgánicos (después de 1.3, al cerrar los óxidos)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4.21. Análisis de la combustión como reacción química: reactivos, productos y energía liberada.</t>
+          <t>1.13. Identificación de reacciones de oxidación y reducción en fenómenos cotidianos.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Escribe y balancea la ecuación de combustión del metano o del etanol, calcula la masa de CO2 producida y relaciona la combustión incompleta con el monóxido de carbono.</t>
+          <t>Reconoce en la oxidación de un clavo, la combustión de una vela y la obtención de un metal a partir de su óxido la ganancia o pérdida de oxígeno, y nombra la sustancia que se oxida y la que se reduce.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Combustión, Estequiometría, Reacciones exotérmicas y endotérmicas</t>
+          <t>Oxidación y reducción, Número de oxidación</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>AU 8, CO 8.5, ENG 6 (Combustión); prerrequisito: Reacciones exotérmicas y endotérmicas (6.°, acción 8)</t>
+          <t>ENG 6, JP 7 (Oxidación y reducción); mover_antes: destino 7.°, hoy en 11.°, sin bloqueos; prerrequisito disponible: Número de oxidación (G05 4.7)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Los tres países enseñan la combustión entre 6.° y 8.5; El Salvador, en 11.°. En 8.° une estequiometría, energía y los contaminantes del aire vistos en 5.°. Se paga con la fusión 15.</t>
+          <t>Inglaterra y Japón enseñan oxidación y reducción en 6.° y 7.°; El Salvador, en 11.°. Encaja tras la formación de óxidos y se trata a nivel cualitativo. Se paga con la fusión 18.</t>
         </is>
       </c>
     </row>
@@ -988,51 +988,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>G08-CIE-U4-4.18, G08-CIE-U4-4.19</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>4. Estequiometría y dispersiones</t>
+          <t>5. Recurso hídrico (después de 5.9)</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>4.18. Demostración experimental de las propiedades coligativas.</t>
+          <t>5.10. Identificación de ácidos y bases con indicadores y análisis de su neutralización.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Comprueba con un experimento el descenso del punto de congelación o el aumento del punto de ebullición al agregar soluto y lo explica con el número de partículas disueltas.</t>
+          <t>Usa un indicador natural (col morada) y papel pH para clasificar productos del hogar en ácidos, neutros o básicos, y comprueba que al mezclar un ácido con una base el pH se acerca a 7.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Propiedades coligativas</t>
+          <t>Indicadores ácido-base, Neutralización y reacciones de los ácidos, Escala de pH</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Propiedades coligativas (4.20 también)</t>
+          <t>ENG 6, JP 5 (Indicadores ácido-base); mover_antes: destino 6.°, hoy en 9.°; bloqueo Escala de pH (7.°); ENG 6, JP 8 (Neutralización y reacciones de los ácidos); mover_antes: destino 7.°, hoy en 9.°; bloqueos Ácidos y bases: propiedades y Ecuación química y su balanceo (7.°, unidad 1)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Demostración y experimentación de las propiedades coligativas son el mismo contenido en dos temas, con un tercero (4.20) de aplicaciones. La fusión paga la acción 1.</t>
+          <t>Dos candidatos con dos países de alto desempeño cada uno. Va en 7.° y no en 6.° porque la escala de pH llega en 7.° (5.9). G09 3.10 queda como profundización. Se paga con la fusión 19.</t>
         </is>
       </c>
     </row>
@@ -1042,51 +1036,45 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>G08-CIE-U4-4.4, G08-CIE-U4-4.5</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4. Estequiometría y dispersiones</t>
+          <t>5. Minerales (después de 5.5)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4.4. Interpretación del número de Avogadro y cálculo de partículas y moles de una sustancia.</t>
+          <t>5.7. Relación entre la estructura y las propiedades de metales, cerámicas y materiales compuestos.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Explica el mol como una cantidad fija de partículas y convierte entre moles y número de partículas en problemas sencillos.</t>
+          <t>Compara la dureza, fragilidad y conductividad de un metal, una cerámica y un material compuesto de uso cotidiano y relaciona cada propiedad con su estructura y con un uso.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Mol y número de Avogadro</t>
+          <t>Metales, cerámicas y materiales compuestos, Sólidos cristalinos y amorfos</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Mol y número de Avogadro (4.10 también)</t>
+          <t>ENG 6, JP 8 (Metales, cerámicas y materiales compuestos); mover_antes: destino 7.°, hoy en 10.°; bloqueo: Sólidos cristalinos y amorfos (8.°, G08 5.4 a 5.6): por eso va en 8.° y no en 7.°</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>El significado del número de Avogadro y su uso en cálculos se enseñan mejor juntos. La fusión paga la acción 3.</t>
+          <t>Inglaterra y Japón lo enseñan en 6.° y 8.°; El Salvador, en 10.° y 11.°. No puede ir en 7.° porque los sólidos cristalinos llegan en 8.°; se ubica tras ellos. Se paga con la fusión 17.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1089,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.12, G08-CIE-U4-4.14</t>
+          <t>G08-CIE-U4-4.18, G08-CIE-U4-4.19</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1120,27 +1108,27 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4.12. Identificación de los tipos de dispersiones químicas en sustancias de uso cotidiano y de sus aplicaciones.</t>
+          <t>4.18. Demostración experimental de las propiedades coligativas.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Identifica disoluciones, coloides y suspensiones en productos del hogar y describe un uso de cada tipo.</t>
+          <t>Comprueba con un experimento el descenso del punto de congelación o el aumento del punto de ebullición al agregar soluto y lo explica con el número de partículas disueltas.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Disoluciones, coloides y suspensiones</t>
+          <t>Propiedades coligativas</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Disoluciones, coloides y suspensiones (4.13 también)</t>
+          <t>fusión: ambos temas trabajan Propiedades coligativas (4.20 también)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>La unidad dedica tres temas a las dispersiones. Identificación y exploración de aplicaciones se unen; la clasificación (4.13) se mantiene. La fusión paga la acción 5.</t>
+          <t>Demostración y experimentación de las propiedades coligativas son el mismo contenido en dos temas, con un tercero (4.20) de aplicaciones. La fusión paga la acción 1.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1143,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.1, G08-CIE-U4-4.3</t>
+          <t>G08-CIE-U4-4.4, G08-CIE-U4-4.5</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1174,27 +1162,27 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4.1. Identificación de las unidades físicas de concentración y de sus aplicaciones cotidianas, industriales y ambientales.</t>
+          <t>4.4. Interpretación del número de Avogadro y cálculo de partículas y moles de una sustancia.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Interpreta la concentración en etiquetas de productos (% m/m, % m/v, ppm) y explica su importancia en un caso ambiental o industrial.</t>
+          <t>Explica el mol como una cantidad fija de partículas y convierte entre moles y número de partículas en problemas sencillos.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Soluto, disolvente y concentración</t>
+          <t>Mol y número de Avogadro</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Soluto, disolvente y concentración (4.2 y 4.15 también)</t>
+          <t>fusión: ambos temas trabajan Mol y número de Avogadro (4.10 también)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Identificar las unidades físicas de concentración y explorar sus aplicaciones son el mismo contenido; el cálculo (4.2) se mantiene aparte. La fusión paga la acción 7.</t>
+          <t>El significado del número de Avogadro y su uso en cálculos se enseñan mejor juntos. La fusión paga la acción 3.</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1197,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U4-4.7, G08-CIE-U4-4.8</t>
+          <t>G08-CIE-U4-4.12, G08-CIE-U4-4.14</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1228,27 +1216,27 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>4.7. Ejecución e interpretación de cálculos estequiométricos para determinar cantidades de sustancia en gramos.</t>
+          <t>4.12. Identificación de los tipos de dispersiones químicas en sustancias de uso cotidiano y de sus aplicaciones.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Calcula la masa de producto o reactivo en una reacción balanceada y juzga si el resultado es razonable.</t>
+          <t>Identifica disoluciones, coloides y suspensiones en productos del hogar y describe un uso de cada tipo.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Estequiometría</t>
+          <t>Disoluciones, coloides y suspensiones</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Estequiometría</t>
+          <t>fusión: ambos temas trabajan Disoluciones, coloides y suspensiones (4.13 también)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Calcular e interpretar el resultado son pasos del mismo procedimiento. La fusión paga la acción 8.</t>
+          <t>La unidad dedica tres temas a las dispersiones. Identificación y exploración de aplicaciones se unen; la clasificación (4.13) se mantiene. La fusión paga la acción 5.</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1251,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U5-5.5, G08-CIE-U5-5.6</t>
+          <t>G08-CIE-U4-4.1, G08-CIE-U4-4.3</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1277,32 +1265,248 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>4. Estequiometría y dispersiones</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4.1. Identificación de las unidades físicas de concentración y de sus aplicaciones cotidianas, industriales y ambientales.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Interpreta la concentración en etiquetas de productos (% m/m, % m/v, ppm) y explica su importancia en un caso ambiental o industrial.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Soluto, disolvente y concentración</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Soluto, disolvente y concentración (4.2 y 4.15 también)</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Identificar las unidades físicas de concentración y explorar sus aplicaciones son el mismo contenido; el cálculo (4.2) se mantiene aparte. La fusión paga la acción 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>G08-CIE-U4-4.7, G08-CIE-U4-4.8</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>4. Estequiometría y dispersiones</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>4.7. Ejecución e interpretación de cálculos estequiométricos para determinar cantidades de sustancia en gramos.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Calcula la masa de producto o reactivo en una reacción balanceada y juzga si el resultado es razonable.</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Estequiometría</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Estequiometría</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Calcular e interpretar el resultado son pasos del mismo procedimiento. La fusión paga la acción 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>G08-CIE-U5-5.5, G08-CIE-U5-5.6</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>5. Minerales</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5.5. Determinación del hábito cristalino de un mineral preparado experimentalmente y reconocimiento de las estructuras cristalinas.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Compara el cristal que obtuvo con imágenes de minerales y describe su forma geométrica y la estructura cristalina que la explica.</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Minerales: composición y estructura cristalina, Sólidos cristalinos y amorfos</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>fusión: ambos temas trabajan Minerales: composición y estructura cristalina y Sólidos cristalinos y amorfos (5.4 también)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>Los temas 5.4 a 5.6 trabajan los mismos dos conceptos. Unir hábito y estructura cristalina libera un tema para la combustión (acción 9).</t>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Los temas 5.4 a 5.6 trabajan los mismos dos conceptos. Unir hábito y estructura cristalina libera, en la misma unidad, el tema de materiales (acción 11).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>G07-CIE-U1-1.9, G07-CIE-U1-1.12</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1. Compuestos inorgánicos</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1.9. Aplicación de nomenclaturas químicas para denominar hidróxidos, oxácidos y oxisales.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Nombra con la nomenclatura sistemática y la tradicional hidróxidos, oxácidos y las oxisales que derivan de ellos, y relaciona el nombre del ácido con el de su sal.</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Compuestos inorgánicos: funciones y nomenclatura</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Compuestos inorgánicos: funciones y nomenclatura (1.3 y 1.6 también)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>La unidad repite un tema de nomenclatura por cada función. Oxácidos y oxisales se nombran con las mismas reglas (-ico/-ato, -oso/-ito). La fusión paga la acción 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>G08-CIE-U4-4.9, G08-CIE-U4-4.11</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4. Estequiometría y dispersiones</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4.9. Identificación de las unidades químicas de concentración en sustancias de uso cotidiano y en procesos industriales.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Interpreta la molaridad indicada en reactivos y productos comerciales y describe un proceso industrial donde controlar la concentración es necesario.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Molaridad y unidades químicas de concentración, Procesos de la industria química</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>fusión: ambos temas trabajan Molaridad y unidades químicas de concentración (4.10 también)</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Es el mismo par identificación + aplicaciones que la fusión 15 resuelve para las unidades físicas; el cálculo (4.10) se mantiene. La fusión paga la acción 10.</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1595,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1414,7 +1618,7 @@
         <v>13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>
@@ -1437,7 +1641,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>
